--- a/docs/Phase0_01_機能一覧.xlsx
+++ b/docs/Phase0_01_機能一覧.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/562294414948a666/ドキュメント/myWeb/RecipeSite/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_AD4D066CA252ABDACC104868B151CE7672EEDF52" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{43F34901-8D4E-4744-AEC2-E338B033774C}"/>
+  <xr:revisionPtr revIDLastSave="52" documentId="11_AD4D066CA252ABDACC104868B151CE7672EEDF52" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{590BF224-41AC-4B37-A1FE-9A57994D2282}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="43095" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Split1" sheetId="1" r:id="rId1"/>
@@ -22,6 +22,226 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+  <si>
+    <t>機能No.</t>
+    <rPh sb="0" eb="2">
+      <t>キノウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>機能名</t>
+    <rPh sb="0" eb="3">
+      <t>キノウメイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>機能詳細</t>
+    <rPh sb="0" eb="4">
+      <t>キノウショウサイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>01</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>クリックしたレシピサムネイルのレシピページに遷移する。</t>
+    <rPh sb="22" eb="24">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>02</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>献立表ページ遷移</t>
+    <rPh sb="0" eb="3">
+      <t>コンダテヒョウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>03</t>
+  </si>
+  <si>
+    <t>04</t>
+  </si>
+  <si>
+    <t>05</t>
+  </si>
+  <si>
+    <t>レシピページ遷移(サムネイル)</t>
+    <rPh sb="6" eb="8">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>レシピページ遷移(本日の献立)</t>
+    <rPh sb="6" eb="8">
+      <t>センイ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ホンジツ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>コンダテ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>レシピ検索機能</t>
+    <rPh sb="3" eb="5">
+      <t>ケンサク</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>キノウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>レシピを探すにあるテキストボックスに入力されたワードにマッチするレシピを検索し結果を表示。
+検索結果ページへ遷移する。</t>
+    <rPh sb="4" eb="5">
+      <t>サガ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>ケンサク</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>ケッカ</t>
+    </rPh>
+    <rPh sb="42" eb="44">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="46" eb="48">
+      <t>ケンサク</t>
+    </rPh>
+    <rPh sb="48" eb="50">
+      <t>ケッカ</t>
+    </rPh>
+    <rPh sb="54" eb="56">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>献立表へリンクをクリックしたときに献立表ページに遷移する。</t>
+    <rPh sb="0" eb="2">
+      <t>コンダテ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ヒョウ</t>
+    </rPh>
+    <rPh sb="17" eb="20">
+      <t>コンダテヒョウ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>本日の献立にあるレシピをクリックしたときにそのレシピページに遷移する。</t>
+    <rPh sb="0" eb="2">
+      <t>ホンジツ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>コンダテ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>タグマッチ機能</t>
+    <rPh sb="5" eb="7">
+      <t>キノウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>タグ一覧にあるタグをクリックしたときに、それに合うレシピを検索し結果を表示。
+検索結果ページへ遷移する。</t>
+    <rPh sb="2" eb="4">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>ケンサク</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>ケッカ</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>ケンサク</t>
+    </rPh>
+    <rPh sb="41" eb="43">
+      <t>ケッカ</t>
+    </rPh>
+    <rPh sb="47" eb="49">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>06</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>レシピをもっと見る機能</t>
+    <rPh sb="7" eb="8">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>キノウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>レシピリストにあるもっと見るボタンを押したとき、画面下にレシピ表示数を増やし、ドラッグで見れるようにする。</t>
+    <rPh sb="12" eb="13">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="24" eb="27">
+      <t>ガメンシタ</t>
+    </rPh>
+    <rPh sb="31" eb="34">
+      <t>ヒョウジスウ</t>
+    </rPh>
+    <rPh sb="35" eb="36">
+      <t>フ</t>
+    </rPh>
+    <rPh sb="44" eb="45">
+      <t>ミ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -50,7 +270,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -58,12 +278,52 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -344,9 +604,91 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1"/>
+  <dimension ref="B2:D8"/>
   <sheetFormatPr defaultRowHeight="18"/>
-  <sheetData/>
+  <cols>
+    <col min="3" max="3" width="28.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="71" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:4">
+      <c r="B2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="2:4">
+      <c r="B3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4">
+      <c r="B4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4">
+      <c r="B5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" ht="54">
+      <c r="B6" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4" ht="68.5" customHeight="1">
+      <c r="B7" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4" ht="36">
+      <c r="B8" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docs/Phase0_01_機能一覧.xlsx
+++ b/docs/Phase0_01_機能一覧.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/562294414948a666/ドキュメント/myWeb/RecipeSite/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="52" documentId="11_AD4D066CA252ABDACC104868B151CE7672EEDF52" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{590BF224-41AC-4B37-A1FE-9A57994D2282}"/>
+  <xr:revisionPtr revIDLastSave="57" documentId="11_AD4D066CA252ABDACC104868B151CE7672EEDF52" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7C3576F7-C5FE-45A4-8A15-7454CA94BD6B}"/>
   <bookViews>
-    <workbookView xWindow="43095" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Split1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t>機能No.</t>
     <rPh sb="0" eb="2">
@@ -238,6 +238,17 @@
     </rPh>
     <rPh sb="44" eb="45">
       <t>ミ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>split02</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>担当split</t>
+    <rPh sb="0" eb="2">
+      <t>タントウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -315,15 +326,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -604,14 +613,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:D8"/>
+  <dimension ref="B2:E8"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="3" max="3" width="28.83203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="71" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:4">
+    <row r="2" spans="2:5">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
@@ -621,8 +631,11 @@
       <c r="D2" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="E2" s="9" t="s">
+        <v>22</v>
+      </c>
     </row>
-    <row r="3" spans="2:4">
+    <row r="3" spans="2:5">
       <c r="B3" s="2" t="s">
         <v>3</v>
       </c>
@@ -632,8 +645,11 @@
       <c r="D3" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="E3" s="9" t="s">
+        <v>21</v>
+      </c>
     </row>
-    <row r="4" spans="2:4">
+    <row r="4" spans="2:5">
       <c r="B4" s="2" t="s">
         <v>5</v>
       </c>
@@ -643,8 +659,9 @@
       <c r="D4" s="1" t="s">
         <v>14</v>
       </c>
+      <c r="E4" s="1"/>
     </row>
-    <row r="5" spans="2:4">
+    <row r="5" spans="2:5">
       <c r="B5" s="2" t="s">
         <v>7</v>
       </c>
@@ -654,8 +671,9 @@
       <c r="D5" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="E5" s="1"/>
     </row>
-    <row r="6" spans="2:4" ht="54">
+    <row r="6" spans="2:5" ht="54">
       <c r="B6" s="3" t="s">
         <v>8</v>
       </c>
@@ -665,8 +683,9 @@
       <c r="D6" s="5" t="s">
         <v>13</v>
       </c>
+      <c r="E6" s="1"/>
     </row>
-    <row r="7" spans="2:4" ht="68.5" customHeight="1">
+    <row r="7" spans="2:5" ht="68.5" customHeight="1">
       <c r="B7" s="3" t="s">
         <v>9</v>
       </c>
@@ -676,17 +695,19 @@
       <c r="D7" s="6" t="s">
         <v>17</v>
       </c>
+      <c r="E7" s="1"/>
     </row>
-    <row r="8" spans="2:4" ht="36">
-      <c r="B8" s="7" t="s">
+    <row r="8" spans="2:5" ht="36">
+      <c r="B8" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="D8" s="8" t="s">
         <v>20</v>
       </c>
+      <c r="E8" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
